--- a/mygui/db/test_report_alh123.xlsx
+++ b/mygui/db/test_report_alh123.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workkkkkk\harvel systems\codes\gui\mygui\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFC39FC-BCFF-426F-85BA-F49C39CECDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703B53CA-31D2-494C-ADB1-50A5AACEE9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="24" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -775,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -827,9 +827,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -845,6 +842,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -929,27 +956,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1257,96 +1263,95 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q114"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.26953125" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" customWidth="1"/>
-    <col min="3" max="3" width="6.08984375" customWidth="1"/>
-    <col min="4" max="4" width="44.6328125" customWidth="1"/>
-    <col min="5" max="5" width="14.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+    <col min="4" max="4" width="44.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="8.26953125" customWidth="1"/>
-    <col min="10" max="10" width="9.6328125" customWidth="1"/>
-    <col min="11" max="11" width="10.08984375" customWidth="1"/>
-    <col min="12" max="12" width="6.36328125" customWidth="1"/>
-    <col min="13" max="13" width="7.90625" customWidth="1"/>
-    <col min="14" max="14" width="7.81640625" customWidth="1"/>
-    <col min="15" max="15" width="8.6328125" customWidth="1"/>
-    <col min="16" max="16" width="9.7265625" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" customWidth="1"/>
-    <col min="18" max="18" width="6.90625" customWidth="1"/>
-    <col min="19" max="19" width="7.54296875" customWidth="1"/>
-    <col min="20" max="20" width="7.81640625" customWidth="1"/>
-    <col min="21" max="21" width="6.36328125" customWidth="1"/>
-    <col min="22" max="22" width="6.54296875" customWidth="1"/>
-    <col min="23" max="23" width="5.90625" customWidth="1"/>
-    <col min="24" max="24" width="7.81640625" customWidth="1"/>
-    <col min="25" max="25" width="7.6328125" customWidth="1"/>
-    <col min="26" max="26" width="7.7265625" customWidth="1"/>
-    <col min="27" max="27" width="6.36328125" customWidth="1"/>
-    <col min="28" max="28" width="7.90625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
+    <col min="12" max="12" width="6.42578125" customWidth="1"/>
+    <col min="13" max="14" width="7.85546875" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.42578125" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" customWidth="1"/>
+    <col min="19" max="19" width="7.5703125" customWidth="1"/>
+    <col min="20" max="20" width="7.85546875" customWidth="1"/>
+    <col min="21" max="21" width="6.42578125" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" customWidth="1"/>
+    <col min="23" max="23" width="5.85546875" customWidth="1"/>
+    <col min="24" max="24" width="7.85546875" customWidth="1"/>
+    <col min="25" max="25" width="7.5703125" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="27" max="27" width="6.42578125" customWidth="1"/>
+    <col min="28" max="28" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="59"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34"/>
       <c r="F2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="62"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G2" s="27"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
       <c r="F3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="63"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G3" s="28"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
       <c r="F4" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="64"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G4" s="29"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="59"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
     </row>
-    <row r="6" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="59"/>
-    </row>
-    <row r="7" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="25" t="s">
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-    </row>
-    <row r="8" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+    </row>
+    <row r="8" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1369,184 +1374,184 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="26">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="35">
         <v>1</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E10" s="17"/>
-      <c r="F10" s="19"/>
+      <c r="F10" s="30"/>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="34"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="27"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="2" t="s">
         <v>131</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="9"/>
+      <c r="F11" s="26"/>
       <c r="G11" s="2"/>
       <c r="H11" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="34"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="26" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="43"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>138</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="34"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="27"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="43"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="2" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="34"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="26" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="43"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="35" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="34"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="27"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="43"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="2" t="s">
         <v>131</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="34"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="26" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="35" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="34"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="27"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="43"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="36"/>
       <c r="D17" s="2" t="s">
         <v>131</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="F17" s="25"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="34"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="26" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="43"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>135</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="34"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="27"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="43"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="36"/>
       <c r="D19" s="2" t="s">
         <v>136</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="F19" s="25"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="34"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="26" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="43"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="F20" s="25"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="34"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="27"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="43"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="36"/>
       <c r="D21" s="2" t="s">
         <v>134</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="34"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="26" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="43"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="35" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="F22" s="25"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="34"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="27"/>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="43"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="36"/>
       <c r="D23" s="2" t="s">
         <v>131</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="F23" s="25"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="27"/>
-      <c r="B24" s="33"/>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="36"/>
+      <c r="B24" s="42"/>
       <c r="C24" s="2" t="s">
         <v>14</v>
       </c>
@@ -1554,14 +1559,14 @@
         <v>15</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="F24" s="25"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="26">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="35">
         <v>2</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="37" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1571,12 +1576,12 @@
         <v>18</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="F25" s="25"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
       <c r="C26" s="2" t="s">
         <v>19</v>
       </c>
@@ -1584,12 +1589,12 @@
         <v>20</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="F26" s="25"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="34"/>
-      <c r="B27" s="35"/>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="43"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
@@ -1597,12 +1602,12 @@
         <v>20</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="F27" s="25"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
       <c r="C28" s="2" t="s">
         <v>22</v>
       </c>
@@ -1610,12 +1615,12 @@
         <v>18</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
       <c r="C29" s="2" t="s">
         <v>23</v>
       </c>
@@ -1623,12 +1628,12 @@
         <v>20</v>
       </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="27"/>
-      <c r="B30" s="29"/>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="36"/>
+      <c r="B30" s="38"/>
       <c r="C30" s="2" t="s">
         <v>24</v>
       </c>
@@ -1636,14 +1641,14 @@
         <v>20</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="26">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="35">
         <v>3</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="37" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -1653,12 +1658,12 @@
         <v>27</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="F31" s="25"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="27"/>
-      <c r="B32" s="29"/>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="36"/>
+      <c r="B32" s="38"/>
       <c r="C32" s="2" t="s">
         <v>28</v>
       </c>
@@ -1666,38 +1671,38 @@
         <v>29</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="F32" s="25"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33" s="26">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="35">
         <v>4</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="35" t="s">
         <v>31</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>129</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="F33" s="25"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A34" s="27"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="27"/>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="36"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="36"/>
       <c r="D34" s="2" t="s">
         <v>130</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="F34" s="25"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -1706,7 +1711,7 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
     </row>
-    <row r="36" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -1715,7 +1720,7 @@
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
     </row>
-    <row r="37" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -1724,7 +1729,7 @@
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
     </row>
-    <row r="38" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -1733,7 +1738,7 @@
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
@@ -1742,38 +1747,38 @@
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A41" s="41" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="41" t="s">
+      <c r="C41" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="49" t="s">
+      <c r="D41" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E41" s="51" t="s">
+      <c r="E41" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="53" t="s">
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="K41" s="53" t="s">
+      <c r="K41" s="62" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="42"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="50"/>
+    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="51"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="59"/>
       <c r="E42" s="16" t="s">
         <v>32</v>
       </c>
@@ -1789,17 +1794,17 @@
       <c r="I42" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J42" s="54"/>
-      <c r="K42" s="54"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A43" s="26">
+      <c r="J42" s="63"/>
+      <c r="K42" s="63"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="35">
         <v>5</v>
       </c>
-      <c r="B43" s="36" t="s">
+      <c r="B43" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="35" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="2" t="s">
@@ -1813,10 +1818,10 @@
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
     </row>
-    <row r="44" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="34"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="27"/>
+    <row r="44" spans="1:11" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="43"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="36"/>
       <c r="D44" s="2" t="s">
         <v>54</v>
       </c>
@@ -1828,10 +1833,10 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="34"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="26" t="s">
+    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="43"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="35" t="s">
         <v>36</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -1845,10 +1850,10 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A46" s="27"/>
-      <c r="B46" s="39"/>
-      <c r="C46" s="27"/>
+    <row r="46" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="36"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="36"/>
       <c r="D46" s="2" t="s">
         <v>104</v>
       </c>
@@ -1860,7 +1865,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -1873,7 +1878,7 @@
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
     </row>
-    <row r="49" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
@@ -1896,12 +1901,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50" s="26"/>
-      <c r="B50" s="36" t="s">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="35"/>
+      <c r="B50" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="39" t="s">
         <v>37</v>
       </c>
       <c r="D50" s="2" t="s">
@@ -1911,10 +1916,10 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51" s="47"/>
-      <c r="B51" s="37"/>
-      <c r="C51" s="31"/>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="56"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="40"/>
       <c r="D51" s="4" t="s">
         <v>102</v>
       </c>
@@ -1922,9 +1927,9 @@
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A52" s="34"/>
-      <c r="B52" s="38"/>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="43"/>
+      <c r="B52" s="47"/>
       <c r="C52" s="2" t="s">
         <v>38</v>
       </c>
@@ -1935,9 +1940,9 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A53" s="34"/>
-      <c r="B53" s="38"/>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="43"/>
+      <c r="B53" s="47"/>
       <c r="C53" s="2" t="s">
         <v>40</v>
       </c>
@@ -1948,10 +1953,10 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A54" s="34"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="30" t="s">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="43"/>
+      <c r="B54" s="47"/>
+      <c r="C54" s="39" t="s">
         <v>42</v>
       </c>
       <c r="D54" s="4" t="s">
@@ -1961,10 +1966,10 @@
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A55" s="34"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="31"/>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="43"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="40"/>
       <c r="D55" s="4" t="s">
         <v>106</v>
       </c>
@@ -1972,9 +1977,9 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A56" s="34"/>
-      <c r="B56" s="38"/>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="43"/>
+      <c r="B56" s="47"/>
       <c r="C56" s="5" t="s">
         <v>43</v>
       </c>
@@ -1985,9 +1990,9 @@
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A57" s="27"/>
-      <c r="B57" s="39"/>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="36"/>
+      <c r="B57" s="48"/>
       <c r="C57" s="4" t="s">
         <v>46</v>
       </c>
@@ -1998,55 +2003,55 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10"/>
-      <c r="B58" s="24"/>
+      <c r="B58" s="23"/>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
     </row>
-    <row r="60" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C60" s="49" t="s">
+      <c r="C60" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="56" t="s">
+      <c r="D60" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E60" s="51" t="s">
+      <c r="E60" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="52"/>
-      <c r="G60" s="52"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="52"/>
-      <c r="J60" s="52"/>
-      <c r="K60" s="52"/>
-      <c r="L60" s="52"/>
-      <c r="M60" s="52"/>
-      <c r="N60" s="52"/>
-      <c r="O60" s="55"/>
-      <c r="P60" s="48" t="s">
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="61"/>
+      <c r="J60" s="61"/>
+      <c r="K60" s="61"/>
+      <c r="L60" s="61"/>
+      <c r="M60" s="61"/>
+      <c r="N60" s="61"/>
+      <c r="O60" s="64"/>
+      <c r="P60" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="Q60" s="41" t="s">
+      <c r="Q60" s="50" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="29" x14ac:dyDescent="0.35">
-      <c r="A61" s="41"/>
-      <c r="B61" s="44" t="s">
+    <row r="61" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="50"/>
+      <c r="B61" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="C61" s="50"/>
-      <c r="D61" s="57"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="66"/>
       <c r="E61" s="16" t="s">
         <v>44</v>
       </c>
@@ -2080,13 +2085,13 @@
       <c r="O61" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="P61" s="42"/>
-      <c r="Q61" s="42"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A62" s="43"/>
-      <c r="B62" s="45"/>
-      <c r="C62" s="30" t="s">
+      <c r="P61" s="51"/>
+      <c r="Q61" s="51"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="52"/>
+      <c r="B62" s="54"/>
+      <c r="C62" s="39" t="s">
         <v>48</v>
       </c>
       <c r="D62" s="6" t="s">
@@ -2106,10 +2111,10 @@
       <c r="P62" s="6"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A63" s="43"/>
-      <c r="B63" s="45"/>
-      <c r="C63" s="31"/>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="52"/>
+      <c r="B63" s="54"/>
+      <c r="C63" s="40"/>
       <c r="D63" s="6" t="s">
         <v>50</v>
       </c>
@@ -2127,10 +2132,10 @@
       <c r="P63" s="6"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A64" s="43"/>
-      <c r="B64" s="45"/>
-      <c r="C64" s="30" t="s">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="52"/>
+      <c r="B64" s="54"/>
+      <c r="C64" s="39" t="s">
         <v>51</v>
       </c>
       <c r="D64" s="6" t="s">
@@ -2150,10 +2155,10 @@
       <c r="P64" s="6"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A65" s="43"/>
-      <c r="B65" s="45"/>
-      <c r="C65" s="31"/>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="52"/>
+      <c r="B65" s="54"/>
+      <c r="C65" s="40"/>
       <c r="D65" s="6" t="s">
         <v>109</v>
       </c>
@@ -2171,10 +2176,10 @@
       <c r="P65" s="6"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A66" s="43"/>
-      <c r="B66" s="45"/>
-      <c r="C66" s="30" t="s">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="52"/>
+      <c r="B66" s="54"/>
+      <c r="C66" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D66" s="6" t="s">
@@ -2194,10 +2199,10 @@
       <c r="P66" s="6"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A67" s="42"/>
-      <c r="B67" s="46"/>
-      <c r="C67" s="31"/>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="51"/>
+      <c r="B67" s="55"/>
+      <c r="C67" s="40"/>
       <c r="D67" s="6" t="s">
         <v>54</v>
       </c>
@@ -2215,7 +2220,7 @@
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="12"/>
       <c r="B68" s="13"/>
       <c r="C68" s="11"/>
@@ -2234,7 +2239,7 @@
       <c r="P68" s="11"/>
       <c r="Q68" s="11"/>
     </row>
-    <row r="69" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="13"/>
       <c r="C69" s="11"/>
@@ -2253,7 +2258,7 @@
       <c r="P69" s="11"/>
       <c r="Q69" s="11"/>
     </row>
-    <row r="70" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="13"/>
       <c r="C70" s="11"/>
@@ -2272,7 +2277,7 @@
       <c r="P70" s="11"/>
       <c r="Q70" s="11"/>
     </row>
-    <row r="71" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="13"/>
       <c r="C71" s="11"/>
@@ -2291,7 +2296,7 @@
       <c r="P71" s="11"/>
       <c r="Q71" s="11"/>
     </row>
-    <row r="72" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="13"/>
       <c r="C72" s="11"/>
@@ -2310,7 +2315,7 @@
       <c r="P72" s="11"/>
       <c r="Q72" s="11"/>
     </row>
-    <row r="73" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="13"/>
       <c r="C73" s="11"/>
@@ -2329,26 +2334,26 @@
       <c r="P73" s="11"/>
       <c r="Q73" s="11"/>
     </row>
-    <row r="74" spans="1:17" ht="29" x14ac:dyDescent="0.35">
-      <c r="A74" s="21" t="s">
+    <row r="74" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F74" s="22" t="s">
+      <c r="F74" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G74" s="23" t="s">
+      <c r="G74" s="22" t="s">
         <v>6</v>
       </c>
       <c r="H74" s="11"/>
@@ -2362,11 +2367,11 @@
       <c r="P74" s="11"/>
       <c r="Q74" s="11"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A75" s="31">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="40">
         <v>6</v>
       </c>
-      <c r="B75" s="40" t="s">
+      <c r="B75" s="49" t="s">
         <v>55</v>
       </c>
       <c r="C75" s="9" t="s">
@@ -2389,9 +2394,9 @@
       <c r="P75" s="11"/>
       <c r="Q75" s="11"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A76" s="34"/>
-      <c r="B76" s="38"/>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="43"/>
+      <c r="B76" s="47"/>
       <c r="C76" s="2" t="s">
         <v>58</v>
       </c>
@@ -2412,10 +2417,10 @@
       <c r="P76" s="11"/>
       <c r="Q76" s="11"/>
     </row>
-    <row r="77" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="34"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="26" t="s">
+    <row r="77" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="43"/>
+      <c r="B77" s="47"/>
+      <c r="C77" s="35" t="s">
         <v>59</v>
       </c>
       <c r="D77" s="2" t="s">
@@ -2435,10 +2440,10 @@
       <c r="P77" s="11"/>
       <c r="Q77" s="11"/>
     </row>
-    <row r="78" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="34"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="27"/>
+    <row r="78" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="43"/>
+      <c r="B78" s="47"/>
+      <c r="C78" s="36"/>
       <c r="D78" s="2" t="s">
         <v>112</v>
       </c>
@@ -2456,10 +2461,10 @@
       <c r="P78" s="11"/>
       <c r="Q78" s="11"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A79" s="34"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="26" t="s">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="43"/>
+      <c r="B79" s="47"/>
+      <c r="C79" s="35" t="s">
         <v>60</v>
       </c>
       <c r="D79" s="2" t="s">
@@ -2479,10 +2484,10 @@
       <c r="P79" s="11"/>
       <c r="Q79" s="11"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A80" s="34"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="27"/>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="43"/>
+      <c r="B80" s="47"/>
+      <c r="C80" s="36"/>
       <c r="D80" s="2" t="s">
         <v>111</v>
       </c>
@@ -2500,9 +2505,9 @@
       <c r="P80" s="11"/>
       <c r="Q80" s="11"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A81" s="34"/>
-      <c r="B81" s="38"/>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="43"/>
+      <c r="B81" s="47"/>
       <c r="C81" s="2" t="s">
         <v>61</v>
       </c>
@@ -2523,10 +2528,10 @@
       <c r="P81" s="11"/>
       <c r="Q81" s="11"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A82" s="34"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="30" t="s">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="43"/>
+      <c r="B82" s="47"/>
+      <c r="C82" s="39" t="s">
         <v>82</v>
       </c>
       <c r="D82" s="2" t="s">
@@ -2546,10 +2551,10 @@
       <c r="P82" s="11"/>
       <c r="Q82" s="11"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A83" s="34"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="31"/>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="43"/>
+      <c r="B83" s="47"/>
+      <c r="C83" s="40"/>
       <c r="D83" s="2" t="s">
         <v>112</v>
       </c>
@@ -2567,10 +2572,10 @@
       <c r="P83" s="11"/>
       <c r="Q83" s="11"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A84" s="34"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="30" t="s">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="43"/>
+      <c r="B84" s="47"/>
+      <c r="C84" s="39" t="s">
         <v>83</v>
       </c>
       <c r="D84" s="2" t="s">
@@ -2589,10 +2594,10 @@
       <c r="P84" s="11"/>
       <c r="Q84" s="11"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A85" s="34"/>
-      <c r="B85" s="38"/>
-      <c r="C85" s="31"/>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="43"/>
+      <c r="B85" s="47"/>
+      <c r="C85" s="40"/>
       <c r="D85" s="2" t="s">
         <v>111</v>
       </c>
@@ -2609,10 +2614,10 @@
       <c r="P85" s="11"/>
       <c r="Q85" s="11"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A86" s="34"/>
-      <c r="B86" s="38"/>
-      <c r="C86" s="30" t="s">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="43"/>
+      <c r="B86" s="47"/>
+      <c r="C86" s="39" t="s">
         <v>84</v>
       </c>
       <c r="D86" s="2" t="s">
@@ -2631,10 +2636,10 @@
       <c r="P86" s="11"/>
       <c r="Q86" s="11"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A87" s="34"/>
-      <c r="B87" s="38"/>
-      <c r="C87" s="31"/>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="43"/>
+      <c r="B87" s="47"/>
+      <c r="C87" s="40"/>
       <c r="D87" s="2" t="s">
         <v>115</v>
       </c>
@@ -2651,9 +2656,9 @@
       <c r="P87" s="11"/>
       <c r="Q87" s="11"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A88" s="34"/>
-      <c r="B88" s="38"/>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="43"/>
+      <c r="B88" s="47"/>
       <c r="C88" s="2" t="s">
         <v>63</v>
       </c>
@@ -2673,18 +2678,18 @@
       <c r="P88" s="11"/>
       <c r="Q88" s="11"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A89" s="34"/>
-      <c r="B89" s="38"/>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="43"/>
+      <c r="B89" s="47"/>
       <c r="C89" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D89" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="20"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="19"/>
       <c r="I89" s="11"/>
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
@@ -2695,9 +2700,9 @@
       <c r="P89" s="11"/>
       <c r="Q89" s="11"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A90" s="34"/>
-      <c r="B90" s="38"/>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" s="43"/>
+      <c r="B90" s="47"/>
       <c r="C90" s="2" t="s">
         <v>64</v>
       </c>
@@ -2708,9 +2713,9 @@
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A91" s="34"/>
-      <c r="B91" s="38"/>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="43"/>
+      <c r="B91" s="47"/>
       <c r="C91" s="2" t="s">
         <v>66</v>
       </c>
@@ -2721,9 +2726,9 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A92" s="34"/>
-      <c r="B92" s="38"/>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="43"/>
+      <c r="B92" s="47"/>
       <c r="C92" s="2" t="s">
         <v>68</v>
       </c>
@@ -2734,9 +2739,9 @@
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A93" s="34"/>
-      <c r="B93" s="38"/>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="43"/>
+      <c r="B93" s="47"/>
       <c r="C93" s="2" t="s">
         <v>70</v>
       </c>
@@ -2747,9 +2752,9 @@
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A94" s="27"/>
-      <c r="B94" s="39"/>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="36"/>
+      <c r="B94" s="48"/>
       <c r="C94" s="2" t="s">
         <v>71</v>
       </c>
@@ -2760,11 +2765,11 @@
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A95" s="26">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="35">
         <v>7</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="37" t="s">
         <v>72</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -2777,9 +2782,9 @@
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A96" s="34"/>
-      <c r="B96" s="32"/>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="43"/>
+      <c r="B96" s="41"/>
       <c r="C96" s="2" t="s">
         <v>74</v>
       </c>
@@ -2790,9 +2795,9 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A97" s="34"/>
-      <c r="B97" s="32"/>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="43"/>
+      <c r="B97" s="41"/>
       <c r="C97" s="2" t="s">
         <v>75</v>
       </c>
@@ -2803,9 +2808,9 @@
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A98" s="27"/>
-      <c r="B98" s="33"/>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="36"/>
+      <c r="B98" s="42"/>
       <c r="C98" s="2" t="s">
         <v>76</v>
       </c>
@@ -2816,14 +2821,14 @@
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
     </row>
-    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A99" s="26">
+    <row r="99" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A99" s="35">
         <v>8</v>
       </c>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C99" s="26" t="s">
+      <c r="C99" s="35" t="s">
         <v>78</v>
       </c>
       <c r="D99" s="2" t="s">
@@ -2833,10 +2838,10 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
     </row>
-    <row r="100" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A100" s="34"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="27"/>
+    <row r="100" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A100" s="43"/>
+      <c r="B100" s="41"/>
+      <c r="C100" s="36"/>
       <c r="D100" s="2" t="s">
         <v>124</v>
       </c>
@@ -2844,10 +2849,10 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
     </row>
-    <row r="101" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A101" s="34"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="26" t="s">
+    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="43"/>
+      <c r="B101" s="41"/>
+      <c r="C101" s="35" t="s">
         <v>79</v>
       </c>
       <c r="D101" s="2" t="s">
@@ -2857,10 +2862,10 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
     </row>
-    <row r="102" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A102" s="34"/>
-      <c r="B102" s="32"/>
-      <c r="C102" s="27"/>
+    <row r="102" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="43"/>
+      <c r="B102" s="41"/>
+      <c r="C102" s="36"/>
       <c r="D102" s="2" t="s">
         <v>126</v>
       </c>
@@ -2868,10 +2873,10 @@
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
     </row>
-    <row r="103" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A103" s="34"/>
-      <c r="B103" s="32"/>
-      <c r="C103" s="26" t="s">
+    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A103" s="43"/>
+      <c r="B103" s="41"/>
+      <c r="C103" s="35" t="s">
         <v>80</v>
       </c>
       <c r="D103" s="2" t="s">
@@ -2881,10 +2886,10 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A104" s="27"/>
-      <c r="B104" s="33"/>
-      <c r="C104" s="27"/>
+    <row r="104" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A104" s="36"/>
+      <c r="B104" s="42"/>
+      <c r="C104" s="36"/>
       <c r="D104" s="2" t="s">
         <v>128</v>
       </c>
@@ -2892,7 +2897,7 @@
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
     </row>
-    <row r="114" ht="27" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="114" ht="27" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="61">
     <mergeCell ref="P60:P61"/>
